--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.25227</v>
+        <v>16.96781</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89346</v>
+        <v>16.65878</v>
       </c>
       <c r="E2" t="n">
-        <v>16.94423</v>
+        <v>16.88851</v>
       </c>
       <c r="F2" t="n">
-        <v>42.73603</v>
+        <v>42.4722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05115</v>
+        <v>0.05132</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83535</v>
+        <v>1.82208</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.25894</v>
+        <v>17.02653</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52322</v>
+        <v>16.79796</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68294</v>
+        <v>16.83774</v>
       </c>
       <c r="F3" t="n">
-        <v>43.45936</v>
+        <v>42.86558</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05073</v>
+        <v>0.04987</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85154</v>
+        <v>1.86754</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.10205</v>
+        <v>16.96131</v>
       </c>
       <c r="D4" t="n">
-        <v>16.91922</v>
+        <v>16.76211</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95378</v>
+        <v>16.86905</v>
       </c>
       <c r="F4" t="n">
-        <v>43.41748</v>
+        <v>42.26562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05023</v>
+        <v>0.05174</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81593</v>
+        <v>1.83773</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.0756</v>
+        <v>17.03872</v>
       </c>
       <c r="D6" t="n">
-        <v>16.23121</v>
+        <v>16.256</v>
       </c>
       <c r="E6" t="n">
-        <v>16.81151</v>
+        <v>16.4951</v>
       </c>
       <c r="F6" t="n">
-        <v>22.22496</v>
+        <v>21.90553</v>
       </c>
       <c r="G6" t="n">
-        <v>34.19825</v>
+        <v>34.49113</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.95963</v>
+        <v>16.84036</v>
       </c>
       <c r="D7" t="n">
-        <v>15.95944</v>
+        <v>16.30635</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79534</v>
+        <v>16.71738</v>
       </c>
       <c r="F7" t="n">
-        <v>22.11817</v>
+        <v>22.2976</v>
       </c>
       <c r="G7" t="n">
-        <v>34.46814</v>
+        <v>34.51228</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.90183</v>
+        <v>17.11082</v>
       </c>
       <c r="D8" t="n">
-        <v>16.30367</v>
+        <v>16.2928</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67373</v>
+        <v>16.64315</v>
       </c>
       <c r="F8" t="n">
-        <v>21.34409</v>
+        <v>22.1234</v>
       </c>
       <c r="G8" t="n">
-        <v>34.50404</v>
+        <v>34.10588</v>
       </c>
     </row>
   </sheetData>
